--- a/products-storage/00-free-dopy-ne-v-podarok/04-reestr-doprabot.xlsx
+++ b/products-storage/00-free-dopy-ne-v-podarok/04-reestr-doprabot.xlsx
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="G5" s="2">
-        <f>СУММ(G2:G10)</f>
+        <f>SUM(G2:G10)</f>
         <v/>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
